--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N74_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N74_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.005801043101</v>
+        <v>6.175942669503913</v>
       </c>
       <c r="D2" t="n">
-        <v>37.41291115324182</v>
+        <v>6.079598062401796</v>
       </c>
       <c r="E2" t="n">
-        <v>13.16288261973883</v>
+        <v>2.138968425707559</v>
       </c>
       <c r="F2" t="n">
-        <v>13.39325660131859</v>
+        <v>2.17640419771427</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>68.50471003811943</v>
+        <v>11.13201538119441</v>
       </c>
       <c r="D3" t="n">
-        <v>68.32153034508387</v>
+        <v>11.10224868107613</v>
       </c>
       <c r="E3" t="n">
-        <v>13.16288261973883</v>
+        <v>2.138968425707559</v>
       </c>
       <c r="F3" t="n">
-        <v>13.39325660131859</v>
+        <v>2.17640419771427</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.87219068585856</v>
+        <v>4.529230986452016</v>
       </c>
       <c r="D4" t="n">
-        <v>27.26456851469522</v>
+        <v>4.430492383637973</v>
       </c>
       <c r="E4" t="n">
-        <v>13.16288261973883</v>
+        <v>2.138968425707559</v>
       </c>
       <c r="F4" t="n">
-        <v>13.39325660131859</v>
+        <v>2.17640419771427</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.54130786413655</v>
+        <v>7.075462527922189</v>
       </c>
       <c r="D5" t="n">
-        <v>43.42397370745711</v>
+        <v>7.05639572746178</v>
       </c>
       <c r="E5" t="n">
-        <v>13.16288261973883</v>
+        <v>2.138968425707559</v>
       </c>
       <c r="F5" t="n">
-        <v>13.39325660131859</v>
+        <v>2.17640419771427</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.56538375861457</v>
+        <v>8.704374860774868</v>
       </c>
       <c r="D6" t="n">
-        <v>53.65458121359198</v>
+        <v>8.718869447208696</v>
       </c>
       <c r="E6" t="n">
-        <v>13.16288261973883</v>
+        <v>2.138968425707559</v>
       </c>
       <c r="F6" t="n">
-        <v>13.39325660131859</v>
+        <v>2.17640419771427</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>44.59713828703634</v>
+        <v>7.247034971643406</v>
       </c>
       <c r="D7" t="n">
-        <v>44.61450113985124</v>
+        <v>7.249856435225827</v>
       </c>
       <c r="E7" t="n">
-        <v>13.16288261973883</v>
+        <v>2.138968425707559</v>
       </c>
       <c r="F7" t="n">
-        <v>13.39325660131859</v>
+        <v>2.17640419771427</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>63.0446746071821</v>
+        <v>10.24475962366709</v>
       </c>
       <c r="D8" t="n">
-        <v>63.39123797531221</v>
+        <v>10.30107617098823</v>
       </c>
       <c r="E8" t="n">
-        <v>13.16288261973883</v>
+        <v>2.138968425707559</v>
       </c>
       <c r="F8" t="n">
-        <v>13.39325660131859</v>
+        <v>2.17640419771427</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
